--- a/24网络技术3班考勤.xlsx
+++ b/24网络技术3班考勤.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="56">
   <si>
     <t>学号</t>
   </si>
@@ -34,6 +34,9 @@
     <t>3.09-理论</t>
   </si>
   <si>
+    <t>3.11-理论</t>
+  </si>
+  <si>
     <t>李奥</t>
   </si>
   <si>
@@ -46,13 +49,13 @@
     <t>刘柯纬</t>
   </si>
   <si>
+    <t>×</t>
+  </si>
+  <si>
     <t>张智献</t>
   </si>
   <si>
     <t>肖笛</t>
-  </si>
-  <si>
-    <t>×</t>
   </si>
   <si>
     <t>宁佳怡</t>
@@ -1343,62 +1346,74 @@
       <c r="E2" t="s">
         <v>4</v>
       </c>
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
       <c r="O2" s="26"/>
       <c r="AF2" s="27"/>
       <c r="AH2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:5">
+    <row r="3" ht="15.75" spans="1:6">
       <c r="A3" s="12">
         <v>2452020005</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <f>100-COUNTIF(D3:AZ3,"×")*3</f>
         <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="1:6">
       <c r="A4" s="11">
         <v>2452020012</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <f>100-COUNTIF(D4:AZ4,"×")*3</f>
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:6">
       <c r="A5" s="12">
         <v>2452020033</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <f>100-COUNTIF(D5:AZ5,"×")*3</f>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:25">
@@ -1406,756 +1421,882 @@
         <v>2452020048</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <f>100-COUNTIF(D6:AZ6,"×")*3</f>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
       </c>
       <c r="Y6" s="27"/>
     </row>
-    <row r="7" ht="15" spans="1:5">
+    <row r="7" ht="15" spans="1:6">
       <c r="A7" s="12">
         <v>2452020059</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <f>110-COUNTIF(D7:AZ7,"×")*3</f>
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" ht="15" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="1:6">
       <c r="A8" s="11">
         <v>2452020062</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8">
         <f>100-COUNTIF(D8:AZ8,"×")*3</f>
         <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:6">
       <c r="A9" s="12">
         <v>2452020068</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9">
         <f>100-COUNTIF(D9:AZ9,"×")*3</f>
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:6">
       <c r="A10" s="11">
         <v>2452020071</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10">
         <f>100-COUNTIF(D10:AZ10,"×")*3</f>
         <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:6">
       <c r="A11" s="11">
         <v>2452020091</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <f t="shared" ref="C11:C25" si="0">100-COUNTIF(D11:AZ11,"×")*3</f>
         <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="12">
         <v>2452020094</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" ht="15" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="11">
         <v>2452020098</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="1:6">
       <c r="A14" s="12">
         <v>2452020105</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:6">
       <c r="A15" s="11">
         <v>2452020117</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="1:6">
       <c r="A16" s="12">
         <v>2452020132</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="11">
         <v>2452020133</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="12">
         <v>2452020143</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="11">
         <v>2452020164</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="12">
         <v>2452020176</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="11">
         <v>2452020203</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="12">
         <v>2452020205</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="1:6">
       <c r="A23" s="11">
         <v>2452020236</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
         <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="1:6">
       <c r="A24" s="12">
         <v>2452020243</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" ht="15" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" ht="15" spans="1:6">
       <c r="A25" s="11">
         <v>2452020253</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
       <c r="D25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" ht="15" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" ht="15" spans="1:6">
       <c r="A26" s="11">
         <v>2452020278</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C26">
         <f t="shared" ref="C26:C47" si="1">100-COUNTIF(D26:AZ26,"×")*3</f>
         <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="12">
         <v>2452020293</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C27">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="1:6">
       <c r="A28" s="11">
         <v>2452020297</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C28">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="D28" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" ht="15" spans="1:6">
       <c r="A29" s="12">
         <v>2452020298</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C29">
         <f t="shared" si="1"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="1:6">
       <c r="A30" s="11">
         <v>2452020306</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C30">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="12">
         <v>2452020309</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C31">
         <f>110-COUNTIF(D31:AZ31,"×")*3</f>
         <v>110</v>
       </c>
       <c r="D31" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="11">
         <v>2452020323</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C32">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="12">
         <v>2452020347</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C33">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="D33" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="11">
         <v>2452020357</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C34">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="D34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" ht="15" spans="1:6">
       <c r="A35" s="12">
         <v>2452020371</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C35">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="D35" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" ht="15" spans="1:6">
       <c r="A36" s="11">
         <v>2452020381</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C36">
         <f t="shared" si="1"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" ht="15" spans="1:6">
       <c r="A37" s="12">
         <v>2452020390</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C37">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D37" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F37" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" ht="15" spans="1:6">
       <c r="A38" s="11">
         <v>2452020397</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C38">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="D38" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E38" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" s="12">
         <v>2452020410</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C39">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="D39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E39" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" ht="15" spans="1:6">
       <c r="A40" s="11">
         <v>2452020421</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C40">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="D40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" ht="15" spans="1:6">
       <c r="A41" s="12">
         <v>2452020424</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C41">
         <f t="shared" si="1"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" ht="15" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" ht="15" spans="1:6">
       <c r="A42" s="11">
         <v>2452020454</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C42">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="D42" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E42" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" ht="15" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" ht="15" spans="1:6">
       <c r="A43" s="12">
         <v>2452020478</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C43">
         <f t="shared" si="1"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E43" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" ht="15" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" ht="15" spans="1:6">
       <c r="A44" s="11">
         <v>2452020484</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C44">
         <f t="shared" si="1"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D44" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E44" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" ht="15" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F44" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" ht="15" spans="1:6">
       <c r="A45" s="12">
         <v>2452020759</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C45">
         <f t="shared" si="1"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E45" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" ht="15" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F45" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" ht="15" spans="1:6">
       <c r="A46" s="11">
         <v>2452020821</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C46">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
       <c r="D46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E46" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" ht="15" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F46" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" s="12">
         <v>2452020828</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C47">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="D47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E47" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="F47" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="48" ht="78" customHeight="1" spans="4:64">
@@ -2169,7 +2310,7 @@
       </c>
       <c r="F48">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G48">
         <f t="shared" si="2"/>
@@ -2406,7 +2547,7 @@
     </row>
     <row r="50" ht="30" spans="8:15">
       <c r="H50" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
@@ -2477,7 +2618,7 @@
     </row>
     <row r="3" ht="24.75" spans="1:4">
       <c r="A3" s="12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="21">
         <f>100-COUNTIF(C3:AZ3,"△")*30</f>
@@ -2488,7 +2629,7 @@
     </row>
     <row r="4" ht="24" spans="1:4">
       <c r="A4" s="11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="21">
         <f t="shared" ref="B4:B49" si="0">100-COUNTIF(C4:AZ4,"△")*30</f>
@@ -2499,7 +2640,7 @@
     </row>
     <row r="5" ht="24" spans="1:5">
       <c r="A5" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="21">
         <f t="shared" si="0"/>
@@ -2511,7 +2652,7 @@
     </row>
     <row r="6" ht="24" spans="1:4">
       <c r="A6" s="11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" s="21">
         <f t="shared" si="0"/>
@@ -2522,7 +2663,7 @@
     </row>
     <row r="7" ht="15" spans="1:2">
       <c r="A7" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B7" s="21">
         <f t="shared" si="0"/>
@@ -2531,7 +2672,7 @@
     </row>
     <row r="8" ht="15" spans="1:2">
       <c r="A8" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="21">
         <f t="shared" si="0"/>
@@ -2540,7 +2681,7 @@
     </row>
     <row r="9" ht="24" spans="1:4">
       <c r="A9" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="21">
         <f t="shared" si="0"/>
@@ -2550,7 +2691,7 @@
     </row>
     <row r="10" ht="24" spans="1:4">
       <c r="A10" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="21">
         <f t="shared" si="0"/>
@@ -2561,7 +2702,7 @@
     </row>
     <row r="11" ht="24" spans="1:5">
       <c r="A11" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B11" s="21">
         <f t="shared" si="0"/>
@@ -2573,7 +2714,7 @@
     </row>
     <row r="12" ht="24" spans="1:4">
       <c r="A12" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="21">
         <f t="shared" si="0"/>
@@ -2583,7 +2724,7 @@
     </row>
     <row r="13" ht="24" spans="1:4">
       <c r="A13" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13" s="21">
         <f t="shared" si="0"/>
@@ -2593,7 +2734,7 @@
     </row>
     <row r="14" ht="24" spans="1:4">
       <c r="A14" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" s="21">
         <f t="shared" si="0"/>
@@ -2603,7 +2744,7 @@
     </row>
     <row r="15" ht="24" spans="1:4">
       <c r="A15" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="21">
         <f t="shared" si="0"/>
@@ -2613,7 +2754,7 @@
     </row>
     <row r="16" ht="24" spans="1:5">
       <c r="A16" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" s="21">
         <f t="shared" si="0"/>
@@ -2625,7 +2766,7 @@
     </row>
     <row r="17" ht="24" spans="1:4">
       <c r="A17" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" s="21">
         <f t="shared" si="0"/>
@@ -2635,7 +2776,7 @@
     </row>
     <row r="18" ht="24" spans="1:4">
       <c r="A18" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="21">
         <f t="shared" si="0"/>
@@ -2645,7 +2786,7 @@
     </row>
     <row r="19" ht="24" spans="1:5">
       <c r="A19" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="21">
         <f t="shared" si="0"/>
@@ -2657,7 +2798,7 @@
     </row>
     <row r="20" ht="24" spans="1:4">
       <c r="A20" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="21">
         <f t="shared" si="0"/>
@@ -2667,7 +2808,7 @@
     </row>
     <row r="21" ht="24" spans="1:4">
       <c r="A21" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" s="21">
         <f t="shared" si="0"/>
@@ -2677,7 +2818,7 @@
     </row>
     <row r="22" ht="15" spans="1:2">
       <c r="A22" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B22" s="21">
         <f t="shared" si="0"/>
@@ -2686,7 +2827,7 @@
     </row>
     <row r="23" ht="15" spans="1:2">
       <c r="A23" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23" s="21">
         <f t="shared" si="0"/>
@@ -2695,7 +2836,7 @@
     </row>
     <row r="24" ht="24" spans="1:5">
       <c r="A24" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" s="21">
         <f t="shared" si="0"/>
@@ -2707,7 +2848,7 @@
     </row>
     <row r="25" ht="24" spans="1:5">
       <c r="A25" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25" s="21">
         <f t="shared" si="0"/>
@@ -2719,7 +2860,7 @@
     </row>
     <row r="26" ht="24" spans="1:5">
       <c r="A26" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" s="21">
         <f t="shared" si="0"/>
@@ -2731,7 +2872,7 @@
     </row>
     <row r="27" ht="24" spans="1:5">
       <c r="A27" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27" s="21">
         <f t="shared" si="0"/>
@@ -2743,7 +2884,7 @@
     </row>
     <row r="28" ht="15" spans="1:2">
       <c r="A28" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" s="21">
         <f t="shared" si="0"/>
@@ -2752,7 +2893,7 @@
     </row>
     <row r="29" ht="15" spans="1:2">
       <c r="A29" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" s="21">
         <f t="shared" si="0"/>
@@ -2761,7 +2902,7 @@
     </row>
     <row r="30" ht="24" spans="1:5">
       <c r="A30" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" s="21">
         <f t="shared" si="0"/>
@@ -2773,7 +2914,7 @@
     </row>
     <row r="31" ht="24" spans="1:5">
       <c r="A31" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" s="21">
         <f t="shared" si="0"/>
@@ -2785,7 +2926,7 @@
     </row>
     <row r="32" ht="24" spans="1:4">
       <c r="A32" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" s="21">
         <f t="shared" si="0"/>
@@ -2796,7 +2937,7 @@
     </row>
     <row r="33" ht="24" spans="1:3">
       <c r="A33" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" s="21">
         <f t="shared" si="0"/>
@@ -2806,7 +2947,7 @@
     </row>
     <row r="34" ht="24" spans="1:5">
       <c r="A34" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" s="21">
         <f t="shared" si="0"/>
@@ -2818,7 +2959,7 @@
     </row>
     <row r="35" ht="24" spans="1:5">
       <c r="A35" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" s="21">
         <f t="shared" si="0"/>
@@ -2830,7 +2971,7 @@
     </row>
     <row r="36" ht="15" spans="1:2">
       <c r="A36" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" s="21">
         <f t="shared" si="0"/>
@@ -2839,7 +2980,7 @@
     </row>
     <row r="37" ht="24" spans="1:5">
       <c r="A37" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" s="21">
         <f t="shared" si="0"/>
@@ -2850,7 +2991,7 @@
     </row>
     <row r="38" ht="24" spans="1:5">
       <c r="A38" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" s="21">
         <f t="shared" si="0"/>
@@ -2862,7 +3003,7 @@
     </row>
     <row r="39" ht="24" spans="1:5">
       <c r="A39" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" s="21">
         <f t="shared" si="0"/>
@@ -2874,7 +3015,7 @@
     </row>
     <row r="40" ht="24" spans="1:5">
       <c r="A40" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" s="21">
         <f t="shared" si="0"/>
@@ -2886,7 +3027,7 @@
     </row>
     <row r="41" ht="24" spans="1:4">
       <c r="A41" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" s="21">
         <f t="shared" si="0"/>
@@ -2896,7 +3037,7 @@
     </row>
     <row r="42" ht="24" spans="1:5">
       <c r="A42" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" s="21">
         <f t="shared" si="0"/>
@@ -2908,7 +3049,7 @@
     </row>
     <row r="43" ht="15" spans="1:2">
       <c r="A43" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" s="21">
         <f t="shared" si="0"/>
@@ -2917,7 +3058,7 @@
     </row>
     <row r="44" ht="24" spans="1:5">
       <c r="A44" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" s="21">
         <f t="shared" si="0"/>
@@ -2929,7 +3070,7 @@
     </row>
     <row r="45" ht="24" spans="1:5">
       <c r="A45" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" s="21">
         <f t="shared" si="0"/>
@@ -2941,7 +3082,7 @@
     </row>
     <row r="46" ht="24" spans="1:5">
       <c r="A46" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" s="21">
         <f t="shared" si="0"/>
@@ -2953,7 +3094,7 @@
     </row>
     <row r="47" ht="24" spans="1:5">
       <c r="A47" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" s="21">
         <f t="shared" si="0"/>
@@ -2965,7 +3106,7 @@
     </row>
     <row r="48" ht="15" spans="1:2">
       <c r="A48" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" s="21">
         <f t="shared" si="0"/>
@@ -2974,7 +3115,7 @@
     </row>
     <row r="49" ht="15" spans="1:2">
       <c r="A49" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" s="21">
         <f t="shared" si="0"/>

--- a/24网络技术3班考勤.xlsx
+++ b/24网络技术3班考勤.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="58">
   <si>
     <t>学号</t>
   </si>
@@ -37,6 +37,12 @@
     <t>3.11-理论</t>
   </si>
   <si>
+    <t>3.16理论</t>
+  </si>
+  <si>
+    <t>3.18理论</t>
+  </si>
+  <si>
     <t>李奥</t>
   </si>
   <si>
@@ -46,10 +52,10 @@
     <t>官长皓</t>
   </si>
   <si>
+    <t>×</t>
+  </si>
+  <si>
     <t>刘柯纬</t>
-  </si>
-  <si>
-    <t>×</t>
   </si>
   <si>
     <t>张智献</t>
@@ -1349,71 +1355,95 @@
       <c r="F2" t="s">
         <v>5</v>
       </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
       <c r="O2" s="26"/>
       <c r="AF2" s="27"/>
       <c r="AH2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:6">
+    <row r="3" ht="15.75" spans="1:8">
       <c r="A3" s="12">
         <v>2452020005</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <f>100-COUNTIF(D3:AZ3,"×")*3</f>
         <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="1:8">
       <c r="A4" s="11">
         <v>2452020012</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <f>100-COUNTIF(D4:AZ4,"×")*3</f>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:8">
       <c r="A5" s="12">
         <v>2452020033</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <f>100-COUNTIF(D5:AZ5,"×")*3</f>
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:25">
@@ -1421,882 +1451,1134 @@
         <v>2452020048</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <f>100-COUNTIF(D6:AZ6,"×")*3</f>
         <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
       </c>
       <c r="Y6" s="27"/>
     </row>
-    <row r="7" ht="15" spans="1:6">
+    <row r="7" ht="15" spans="1:8">
       <c r="A7" s="12">
         <v>2452020059</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <f>110-COUNTIF(D7:AZ7,"×")*3</f>
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" ht="15" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="1:8">
       <c r="A8" s="11">
         <v>2452020062</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8">
         <f>100-COUNTIF(D8:AZ8,"×")*3</f>
         <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:8">
       <c r="A9" s="12">
         <v>2452020068</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9">
         <f>100-COUNTIF(D9:AZ9,"×")*3</f>
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:8">
       <c r="A10" s="11">
         <v>2452020071</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10">
         <f>100-COUNTIF(D10:AZ10,"×")*3</f>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:8">
       <c r="A11" s="11">
         <v>2452020091</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11">
         <f t="shared" ref="C11:C25" si="0">100-COUNTIF(D11:AZ11,"×")*3</f>
         <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:8">
       <c r="A12" s="12">
         <v>2452020094</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:8">
       <c r="A13" s="11">
         <v>2452020098</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="1:8">
       <c r="A14" s="12">
         <v>2452020105</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:8">
       <c r="A15" s="11">
         <v>2452020117</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="1:8">
       <c r="A16" s="12">
         <v>2452020132</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" ht="15" spans="1:8">
       <c r="A17" s="11">
         <v>2452020133</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:8">
       <c r="A18" s="12">
         <v>2452020143</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" ht="15" spans="1:8">
       <c r="A19" s="11">
         <v>2452020164</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G19" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="1:8">
       <c r="A20" s="12">
         <v>2452020176</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" ht="15" spans="1:8">
       <c r="A21" s="11">
         <v>2452020203</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G21" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="1:8">
       <c r="A22" s="12">
         <v>2452020205</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G22" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="1:8">
       <c r="A23" s="11">
         <v>2452020236</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
         <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G23" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="1:8">
       <c r="A24" s="12">
         <v>2452020243</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" ht="15" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" ht="15" spans="1:8">
       <c r="A25" s="11">
         <v>2452020253</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G25" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" ht="15" spans="1:8">
       <c r="A26" s="11">
         <v>2452020278</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C26">
         <f t="shared" ref="C26:C47" si="1">100-COUNTIF(D26:AZ26,"×")*3</f>
         <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G26" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" ht="15" spans="1:8">
       <c r="A27" s="12">
         <v>2452020293</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C27">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="1:8">
       <c r="A28" s="11">
         <v>2452020297</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C28">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G28" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" ht="15" spans="1:8">
       <c r="A29" s="12">
         <v>2452020298</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C29">
         <f t="shared" si="1"/>
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G29" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="1:8">
       <c r="A30" s="11">
         <v>2452020306</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C30">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" ht="15" spans="1:8">
       <c r="A31" s="12">
         <v>2452020309</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C31">
         <f>110-COUNTIF(D31:AZ31,"×")*3</f>
         <v>110</v>
       </c>
       <c r="D31" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G31" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" ht="15" spans="1:8">
       <c r="A32" s="11">
         <v>2452020323</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C32">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" ht="15" spans="1:8">
       <c r="A33" s="12">
         <v>2452020347</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C33">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G33" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" ht="15" spans="1:8">
       <c r="A34" s="11">
         <v>2452020357</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C34">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="D34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" ht="15" spans="1:8">
       <c r="A35" s="12">
         <v>2452020371</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C35">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="D35" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G35" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" ht="15" spans="1:8">
       <c r="A36" s="11">
         <v>2452020381</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C36">
         <f t="shared" si="1"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" ht="15" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G36" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="12">
         <v>2452020390</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C37">
         <f t="shared" si="1"/>
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D37" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" ht="15" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" ht="15" spans="1:8">
       <c r="A38" s="11">
         <v>2452020397</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C38">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G38" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" ht="15" spans="1:8">
       <c r="A39" s="12">
         <v>2452020410</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C39">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="D39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F39" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G39" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" ht="15" spans="1:8">
       <c r="A40" s="11">
         <v>2452020421</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C40">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="D40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E40" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G40" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" ht="15" spans="1:8">
       <c r="A41" s="12">
         <v>2452020424</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C41">
         <f t="shared" si="1"/>
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F41" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" ht="15" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G41" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="11">
         <v>2452020454</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C42">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D42" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" ht="15" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G42" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="12">
         <v>2452020478</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C43">
         <f t="shared" si="1"/>
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F43" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" ht="15" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G43" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="11">
         <v>2452020484</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C44">
         <f t="shared" si="1"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D44" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F44" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" ht="15" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G44" t="s">
+        <v>9</v>
+      </c>
+      <c r="H44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" ht="15" spans="1:8">
       <c r="A45" s="12">
         <v>2452020759</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C45">
         <f t="shared" si="1"/>
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" ht="15" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G45" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" ht="15" spans="1:8">
       <c r="A46" s="11">
         <v>2452020821</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C46">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
       <c r="D46" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E46" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F46" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" ht="15" spans="1:8">
       <c r="A47" s="12">
         <v>2452020828</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C47">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="D47" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E47" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F47" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="G47" t="s">
+        <v>9</v>
+      </c>
+      <c r="H47" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="48" ht="78" customHeight="1" spans="4:64">
@@ -2314,11 +2596,11 @@
       </c>
       <c r="G48">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H48">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I48">
         <f t="shared" si="2"/>
@@ -2547,7 +2829,7 @@
     </row>
     <row r="50" ht="30" spans="8:15">
       <c r="H50" s="25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
@@ -2618,7 +2900,7 @@
     </row>
     <row r="3" ht="24.75" spans="1:4">
       <c r="A3" s="12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="21">
         <f>100-COUNTIF(C3:AZ3,"△")*30</f>
@@ -2629,7 +2911,7 @@
     </row>
     <row r="4" ht="24" spans="1:4">
       <c r="A4" s="11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="21">
         <f t="shared" ref="B4:B49" si="0">100-COUNTIF(C4:AZ4,"△")*30</f>
@@ -2640,7 +2922,7 @@
     </row>
     <row r="5" ht="24" spans="1:5">
       <c r="A5" s="12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B5" s="21">
         <f t="shared" si="0"/>
@@ -2652,7 +2934,7 @@
     </row>
     <row r="6" ht="24" spans="1:4">
       <c r="A6" s="11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" s="21">
         <f t="shared" si="0"/>
@@ -2663,7 +2945,7 @@
     </row>
     <row r="7" ht="15" spans="1:2">
       <c r="A7" s="12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="21">
         <f t="shared" si="0"/>
@@ -2672,7 +2954,7 @@
     </row>
     <row r="8" ht="15" spans="1:2">
       <c r="A8" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B8" s="21">
         <f t="shared" si="0"/>
@@ -2681,7 +2963,7 @@
     </row>
     <row r="9" ht="24" spans="1:4">
       <c r="A9" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" s="21">
         <f t="shared" si="0"/>
@@ -2691,7 +2973,7 @@
     </row>
     <row r="10" ht="24" spans="1:4">
       <c r="A10" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" s="21">
         <f t="shared" si="0"/>
@@ -2702,7 +2984,7 @@
     </row>
     <row r="11" ht="24" spans="1:5">
       <c r="A11" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B11" s="21">
         <f t="shared" si="0"/>
@@ -2714,7 +2996,7 @@
     </row>
     <row r="12" ht="24" spans="1:4">
       <c r="A12" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" s="21">
         <f t="shared" si="0"/>
@@ -2724,7 +3006,7 @@
     </row>
     <row r="13" ht="24" spans="1:4">
       <c r="A13" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13" s="21">
         <f t="shared" si="0"/>
@@ -2734,7 +3016,7 @@
     </row>
     <row r="14" ht="24" spans="1:4">
       <c r="A14" s="11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B14" s="21">
         <f t="shared" si="0"/>
@@ -2744,7 +3026,7 @@
     </row>
     <row r="15" ht="24" spans="1:4">
       <c r="A15" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B15" s="21">
         <f t="shared" si="0"/>
@@ -2754,7 +3036,7 @@
     </row>
     <row r="16" ht="24" spans="1:5">
       <c r="A16" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B16" s="21">
         <f t="shared" si="0"/>
@@ -2766,7 +3048,7 @@
     </row>
     <row r="17" ht="24" spans="1:4">
       <c r="A17" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B17" s="21">
         <f t="shared" si="0"/>
@@ -2776,7 +3058,7 @@
     </row>
     <row r="18" ht="24" spans="1:4">
       <c r="A18" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B18" s="21">
         <f t="shared" si="0"/>
@@ -2786,7 +3068,7 @@
     </row>
     <row r="19" ht="24" spans="1:5">
       <c r="A19" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B19" s="21">
         <f t="shared" si="0"/>
@@ -2798,7 +3080,7 @@
     </row>
     <row r="20" ht="24" spans="1:4">
       <c r="A20" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B20" s="21">
         <f t="shared" si="0"/>
@@ -2808,7 +3090,7 @@
     </row>
     <row r="21" ht="24" spans="1:4">
       <c r="A21" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B21" s="21">
         <f t="shared" si="0"/>
@@ -2818,7 +3100,7 @@
     </row>
     <row r="22" ht="15" spans="1:2">
       <c r="A22" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B22" s="21">
         <f t="shared" si="0"/>
@@ -2827,7 +3109,7 @@
     </row>
     <row r="23" ht="15" spans="1:2">
       <c r="A23" s="12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B23" s="21">
         <f t="shared" si="0"/>
@@ -2836,7 +3118,7 @@
     </row>
     <row r="24" ht="24" spans="1:5">
       <c r="A24" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B24" s="21">
         <f t="shared" si="0"/>
@@ -2848,7 +3130,7 @@
     </row>
     <row r="25" ht="24" spans="1:5">
       <c r="A25" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B25" s="21">
         <f t="shared" si="0"/>
@@ -2860,7 +3142,7 @@
     </row>
     <row r="26" ht="24" spans="1:5">
       <c r="A26" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B26" s="21">
         <f t="shared" si="0"/>
@@ -2872,7 +3154,7 @@
     </row>
     <row r="27" ht="24" spans="1:5">
       <c r="A27" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B27" s="21">
         <f t="shared" si="0"/>
@@ -2884,7 +3166,7 @@
     </row>
     <row r="28" ht="15" spans="1:2">
       <c r="A28" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B28" s="21">
         <f t="shared" si="0"/>
@@ -2893,7 +3175,7 @@
     </row>
     <row r="29" ht="15" spans="1:2">
       <c r="A29" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B29" s="21">
         <f t="shared" si="0"/>
@@ -2902,7 +3184,7 @@
     </row>
     <row r="30" ht="24" spans="1:5">
       <c r="A30" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B30" s="21">
         <f t="shared" si="0"/>
@@ -2914,7 +3196,7 @@
     </row>
     <row r="31" ht="24" spans="1:5">
       <c r="A31" s="12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B31" s="21">
         <f t="shared" si="0"/>
@@ -2926,7 +3208,7 @@
     </row>
     <row r="32" ht="24" spans="1:4">
       <c r="A32" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B32" s="21">
         <f t="shared" si="0"/>
@@ -2937,7 +3219,7 @@
     </row>
     <row r="33" ht="24" spans="1:3">
       <c r="A33" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B33" s="21">
         <f t="shared" si="0"/>
@@ -2947,7 +3229,7 @@
     </row>
     <row r="34" ht="24" spans="1:5">
       <c r="A34" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B34" s="21">
         <f t="shared" si="0"/>
@@ -2959,7 +3241,7 @@
     </row>
     <row r="35" ht="24" spans="1:5">
       <c r="A35" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B35" s="21">
         <f t="shared" si="0"/>
@@ -2971,7 +3253,7 @@
     </row>
     <row r="36" ht="15" spans="1:2">
       <c r="A36" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B36" s="21">
         <f t="shared" si="0"/>
@@ -2980,7 +3262,7 @@
     </row>
     <row r="37" ht="24" spans="1:5">
       <c r="A37" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B37" s="21">
         <f t="shared" si="0"/>
@@ -2991,7 +3273,7 @@
     </row>
     <row r="38" ht="24" spans="1:5">
       <c r="A38" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B38" s="21">
         <f t="shared" si="0"/>
@@ -3003,7 +3285,7 @@
     </row>
     <row r="39" ht="24" spans="1:5">
       <c r="A39" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B39" s="21">
         <f t="shared" si="0"/>
@@ -3015,7 +3297,7 @@
     </row>
     <row r="40" ht="24" spans="1:5">
       <c r="A40" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B40" s="21">
         <f t="shared" si="0"/>
@@ -3027,7 +3309,7 @@
     </row>
     <row r="41" ht="24" spans="1:4">
       <c r="A41" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B41" s="21">
         <f t="shared" si="0"/>
@@ -3037,7 +3319,7 @@
     </row>
     <row r="42" ht="24" spans="1:5">
       <c r="A42" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B42" s="21">
         <f t="shared" si="0"/>
@@ -3049,7 +3331,7 @@
     </row>
     <row r="43" ht="15" spans="1:2">
       <c r="A43" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B43" s="21">
         <f t="shared" si="0"/>
@@ -3058,7 +3340,7 @@
     </row>
     <row r="44" ht="24" spans="1:5">
       <c r="A44" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B44" s="21">
         <f t="shared" si="0"/>
@@ -3070,7 +3352,7 @@
     </row>
     <row r="45" ht="24" spans="1:5">
       <c r="A45" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B45" s="21">
         <f t="shared" si="0"/>
@@ -3082,7 +3364,7 @@
     </row>
     <row r="46" ht="24" spans="1:5">
       <c r="A46" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B46" s="21">
         <f t="shared" si="0"/>
@@ -3094,7 +3376,7 @@
     </row>
     <row r="47" ht="24" spans="1:5">
       <c r="A47" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B47" s="21">
         <f t="shared" si="0"/>
@@ -3106,7 +3388,7 @@
     </row>
     <row r="48" ht="15" spans="1:2">
       <c r="A48" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B48" s="21">
         <f t="shared" si="0"/>
@@ -3115,7 +3397,7 @@
     </row>
     <row r="49" ht="15" spans="1:2">
       <c r="A49" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B49" s="21">
         <f t="shared" si="0"/>

--- a/24网络技术3班考勤.xlsx
+++ b/24网络技术3班考勤.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2026\教学\3班\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1024B5E9-C8A0-41E8-A209-5083868E6423}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="考勤" sheetId="3" r:id="rId1"/>
@@ -18,20 +12,12 @@
     <sheet name="实验报告" sheetId="5" r:id="rId3"/>
     <sheet name="打扫卫生" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="64">
   <si>
     <t>学号</t>
   </si>
@@ -66,157 +52,14 @@
     <t>3.30理论</t>
   </si>
   <si>
-    <t>李奥</t>
-  </si>
-  <si>
-    <t>√</t>
-  </si>
-  <si>
-    <t>官长皓</t>
-  </si>
-  <si>
-    <t>×</t>
-  </si>
-  <si>
-    <t>刘柯纬</t>
-  </si>
-  <si>
-    <t>张智献</t>
-  </si>
-  <si>
-    <t>肖笛</t>
-  </si>
-  <si>
-    <t>宁佳怡</t>
-  </si>
-  <si>
-    <t>宋端祥</t>
-  </si>
-  <si>
-    <t>孙赫</t>
-  </si>
-  <si>
-    <t>周欣慧</t>
-  </si>
-  <si>
-    <t>孔繁浩</t>
-  </si>
-  <si>
-    <t>王淑雨</t>
-  </si>
-  <si>
-    <t>刘建平</t>
-  </si>
-  <si>
-    <t>李志远</t>
-  </si>
-  <si>
-    <t>李雨欣</t>
-  </si>
-  <si>
-    <t>江春阳</t>
-  </si>
-  <si>
-    <t>黄一坤</t>
-  </si>
-  <si>
-    <t>朱锦涛</t>
-  </si>
-  <si>
-    <t>姜立敏</t>
-  </si>
-  <si>
-    <t>张在满</t>
-  </si>
-  <si>
-    <t>马圣涵</t>
-  </si>
-  <si>
-    <t>孙蓓</t>
-  </si>
-  <si>
-    <t>陈金腾</t>
-  </si>
-  <si>
-    <t>王安达</t>
-  </si>
-  <si>
-    <t>石文凯</t>
-  </si>
-  <si>
-    <t>祁志一</t>
-  </si>
-  <si>
-    <t>梁亚伟</t>
-  </si>
-  <si>
-    <t>田光宁</t>
-  </si>
-  <si>
-    <t>高明玉</t>
-  </si>
-  <si>
-    <t>崔斐艳</t>
-  </si>
-  <si>
-    <t>翟文铄</t>
-  </si>
-  <si>
-    <t>刘佳鹏</t>
-  </si>
-  <si>
-    <t>张婧</t>
-  </si>
-  <si>
-    <t>王化坤</t>
-  </si>
-  <si>
-    <t>刘存铎</t>
-  </si>
-  <si>
-    <t>李有梁</t>
-  </si>
-  <si>
-    <t>陈时</t>
-  </si>
-  <si>
-    <t>于米朵</t>
-  </si>
-  <si>
-    <t>张初晨</t>
-  </si>
-  <si>
-    <t>刘倩惠</t>
-  </si>
-  <si>
-    <t>张顺</t>
-  </si>
-  <si>
-    <t>刘明义</t>
-  </si>
-  <si>
-    <t>郝江涛</t>
-  </si>
-  <si>
-    <t>侯明幸</t>
-  </si>
-  <si>
-    <t>葛欣宇</t>
-  </si>
-  <si>
-    <t>刘雨蒙</t>
-  </si>
-  <si>
-    <t>√、正常、△、迟到、○早退、×缺勤</t>
-  </si>
-  <si>
-    <t>高顼研</t>
-  </si>
-  <si>
-    <t>夹梦娅</t>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>4</t>
     </r>
     <r>
@@ -224,24 +67,180 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>.01实验</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>4.08实验</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.09实验</t>
+  </si>
+  <si>
+    <t>李奥</t>
+  </si>
+  <si>
+    <t>√</t>
+  </si>
+  <si>
+    <t>官长皓</t>
+  </si>
+  <si>
+    <t>×</t>
+  </si>
+  <si>
+    <t>刘柯纬</t>
+  </si>
+  <si>
+    <t>张智献</t>
+  </si>
+  <si>
+    <t>肖笛</t>
+  </si>
+  <si>
+    <t>宁佳怡</t>
+  </si>
+  <si>
+    <t>宋端祥</t>
+  </si>
+  <si>
+    <t>孙赫</t>
+  </si>
+  <si>
+    <t>周欣慧</t>
+  </si>
+  <si>
+    <t>孔繁浩</t>
+  </si>
+  <si>
+    <t>王淑雨</t>
+  </si>
+  <si>
+    <t>刘建平</t>
+  </si>
+  <si>
+    <t>李志远</t>
+  </si>
+  <si>
+    <t>李雨欣</t>
+  </si>
+  <si>
+    <t>江春阳</t>
+  </si>
+  <si>
+    <t>黄一坤</t>
+  </si>
+  <si>
+    <t>朱锦涛</t>
+  </si>
+  <si>
+    <t>姜立敏</t>
+  </si>
+  <si>
+    <t>张在满</t>
+  </si>
+  <si>
+    <t>马圣涵</t>
+  </si>
+  <si>
+    <t>孙蓓</t>
+  </si>
+  <si>
+    <t>陈金腾</t>
+  </si>
+  <si>
+    <t>王安达</t>
+  </si>
+  <si>
+    <t>石文凯</t>
+  </si>
+  <si>
+    <t>祁志一</t>
+  </si>
+  <si>
+    <t>梁亚伟</t>
+  </si>
+  <si>
+    <t>田光宁</t>
+  </si>
+  <si>
+    <t>高明玉</t>
+  </si>
+  <si>
+    <t>崔斐艳</t>
+  </si>
+  <si>
+    <t>翟文铄</t>
+  </si>
+  <si>
+    <t>刘佳鹏</t>
+  </si>
+  <si>
+    <t>张婧</t>
+  </si>
+  <si>
+    <t>王化坤</t>
+  </si>
+  <si>
+    <t>刘存铎</t>
+  </si>
+  <si>
+    <t>李有梁</t>
+  </si>
+  <si>
+    <t>陈时</t>
+  </si>
+  <si>
+    <t>于米朵</t>
+  </si>
+  <si>
+    <t>张初晨</t>
+  </si>
+  <si>
+    <t>刘倩惠</t>
+  </si>
+  <si>
+    <t>张顺</t>
+  </si>
+  <si>
+    <t>刘明义</t>
+  </si>
+  <si>
+    <t>郝江涛</t>
+  </si>
+  <si>
+    <t>侯明幸</t>
+  </si>
+  <si>
+    <t>葛欣宇</t>
+  </si>
+  <si>
+    <t>刘雨蒙</t>
+  </si>
+  <si>
+    <t>√、正常、△、迟到、○早退、×缺勤</t>
+  </si>
+  <si>
+    <t>高顼研</t>
+  </si>
+  <si>
+    <t>夹梦娅</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,39 +257,39 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="9"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF00B050"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF333333"/>
+      <color theme="6" tint="0.399639881588183"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="6" tint="0.39963988158818325"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -304,6 +303,12 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -321,27 +326,162 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -351,18 +491,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF5F5F5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F5F5"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -418,88 +738,379 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -757,33 +1368,33 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:BL50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="27"/>
+    <row r="2" spans="1:34">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="23"/>
       <c r="D2" t="s">
         <v>3</v>
       </c>
@@ -808,1908 +1419,2046 @@
       <c r="K2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="M2" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="O2" s="20"/>
-      <c r="AF2" s="21"/>
-      <c r="AH2" s="21"/>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A3" s="10">
+      <c r="L2" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="29"/>
+      <c r="AF2" s="28"/>
+      <c r="AH2" s="28"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="5">
         <v>2452020005</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>11</v>
+      <c r="B3" s="24" t="s">
+        <v>14</v>
       </c>
       <c r="C3">
         <f>100-COUNTIF(D3:AZ3,"×")*3</f>
         <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A4" s="9">
+        <v>15</v>
+      </c>
+      <c r="N3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="4">
         <v>2452020012</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>13</v>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="C4">
         <f>100-COUNTIF(D4:AZ4,"×")*3</f>
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A5" s="10">
+        <v>17</v>
+      </c>
+      <c r="N4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="5">
         <v>2452020033</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>15</v>
+      <c r="B5" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C5">
         <f>100-COUNTIF(D5:AZ5,"×")*3</f>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A6" s="9">
+        <v>17</v>
+      </c>
+      <c r="N5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6" s="4">
         <v>2452020048</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>16</v>
+      <c r="B6" s="25" t="s">
+        <v>19</v>
       </c>
       <c r="C6">
         <f>100-COUNTIF(D6:AZ6,"×")*3</f>
         <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M6" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y6" s="21"/>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A7" s="10">
+        <v>15</v>
+      </c>
+      <c r="N6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y6" s="28"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="5">
         <v>2452020059</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>17</v>
+      <c r="B7" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="C7">
         <f>110-COUNTIF(D7:AZ7,"×")*3</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A8" s="9">
+        <v>17</v>
+      </c>
+      <c r="N7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="1:14">
+      <c r="A8" s="4">
         <v>2452020062</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>18</v>
+      <c r="B8" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="C8">
         <f>100-COUNTIF(D8:AZ8,"×")*3</f>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A9" s="10">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:14">
+      <c r="A9" s="5">
         <v>2452020068</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>19</v>
+      <c r="B9" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="C9">
         <f>100-COUNTIF(D9:AZ9,"×")*3</f>
         <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A10" s="9">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:14">
+      <c r="A10" s="4">
         <v>2452020071</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>20</v>
+      <c r="B10" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="C10">
         <f>100-COUNTIF(D10:AZ10,"×")*3</f>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A11" s="9">
+        <v>17</v>
+      </c>
+      <c r="N10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:14">
+      <c r="A11" s="4">
         <v>2452020091</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>21</v>
+      <c r="B11" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="C11">
         <f t="shared" ref="C11:C25" si="0">100-COUNTIF(D11:AZ11,"×")*3</f>
         <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A12" s="10">
+        <v>15</v>
+      </c>
+      <c r="N11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:14">
+      <c r="A12" s="5">
         <v>2452020094</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>22</v>
+      <c r="B12" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A13" s="9">
+        <v>15</v>
+      </c>
+      <c r="N12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:14">
+      <c r="A13" s="4">
         <v>2452020098</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>23</v>
+      <c r="B13" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A14" s="10">
+        <v>15</v>
+      </c>
+      <c r="N13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="1:14">
+      <c r="A14" s="5">
         <v>2452020105</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>24</v>
+      <c r="B14" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A15" s="9">
+        <v>15</v>
+      </c>
+      <c r="N14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:14">
+      <c r="A15" s="4">
         <v>2452020117</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>25</v>
+      <c r="B15" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A16" s="10">
+        <v>17</v>
+      </c>
+      <c r="N15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="1:14">
+      <c r="A16" s="5">
         <v>2452020132</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>26</v>
+      <c r="B16" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="9">
+        <v>15</v>
+      </c>
+      <c r="N16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" ht="15" spans="1:14">
+      <c r="A17" s="4">
         <v>2452020133</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>27</v>
+      <c r="B17" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="10">
+        <v>15</v>
+      </c>
+      <c r="N17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:14">
+      <c r="A18" s="5">
         <v>2452020143</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>28</v>
+      <c r="B18" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="9">
+        <v>15</v>
+      </c>
+      <c r="N18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" ht="15" spans="1:14">
+      <c r="A19" s="4">
         <v>2452020164</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>29</v>
+      <c r="B19" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="10">
+        <v>15</v>
+      </c>
+      <c r="N19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="5">
         <v>2452020176</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>30</v>
+      <c r="B20" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="9">
+        <v>15</v>
+      </c>
+      <c r="N20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="4">
         <v>2452020203</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>31</v>
+      <c r="B21" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M21" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="10">
+        <v>15</v>
+      </c>
+      <c r="N21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="5">
         <v>2452020205</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>32</v>
+      <c r="B22" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M22" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="9">
+        <v>15</v>
+      </c>
+      <c r="N22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="1:14">
+      <c r="A23" s="4">
         <v>2452020236</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>33</v>
+      <c r="B23" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="10">
+        <v>17</v>
+      </c>
+      <c r="N23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="1:14">
+      <c r="A24" s="5">
         <v>2452020243</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>34</v>
+      <c r="B24" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="9">
+        <v>17</v>
+      </c>
+      <c r="N24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="4">
         <v>2452020253</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>35</v>
+      <c r="B25" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E25" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K25" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="9">
+        <v>17</v>
+      </c>
+      <c r="N25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="4">
         <v>2452020278</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>36</v>
+      <c r="B26" s="25" t="s">
+        <v>39</v>
       </c>
       <c r="C26">
         <f t="shared" ref="C26:C47" si="1">100-COUNTIF(D26:AZ26,"×")*3</f>
         <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="10">
+        <v>15</v>
+      </c>
+      <c r="N26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="5">
         <v>2452020293</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>37</v>
+      <c r="B27" s="24" t="s">
+        <v>40</v>
       </c>
       <c r="C27">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M27" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="9">
+        <v>15</v>
+      </c>
+      <c r="N27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="4">
         <v>2452020297</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>38</v>
+      <c r="B28" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="C28">
         <f t="shared" si="1"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="10">
+        <v>15</v>
+      </c>
+      <c r="N28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" ht="15" spans="1:14">
+      <c r="A29" s="5">
         <v>2452020298</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>39</v>
+      <c r="B29" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="C29">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G29" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H29" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J29" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M29" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="9">
+        <v>15</v>
+      </c>
+      <c r="N29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="1:14">
+      <c r="A30" s="4">
         <v>2452020306</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>40</v>
+      <c r="B30" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="C30">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="D30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M30" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="10">
+        <v>17</v>
+      </c>
+      <c r="N30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" ht="15" spans="1:14">
+      <c r="A31" s="5">
         <v>2452020309</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>41</v>
+      <c r="B31" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="C31">
         <f>110-COUNTIF(D31:AZ31,"×")*3</f>
         <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I31" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M31" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="9">
+        <v>15</v>
+      </c>
+      <c r="N31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" ht="15" spans="1:14">
+      <c r="A32" s="4">
         <v>2452020323</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>42</v>
+      <c r="B32" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="C32">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>15</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A33" s="10">
+        <v>15</v>
+      </c>
+      <c r="N32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" ht="15" spans="1:14">
+      <c r="A33" s="5">
         <v>2452020347</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>43</v>
+      <c r="B33" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="C33">
         <f t="shared" si="1"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D33" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E33" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J33" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M33" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A34" s="9">
+        <v>15</v>
+      </c>
+      <c r="N33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" ht="15" spans="1:14">
+      <c r="A34" s="4">
         <v>2452020357</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>44</v>
+      <c r="B34" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="C34">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E34" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I34" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J34" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A35" s="10">
+        <v>17</v>
+      </c>
+      <c r="N34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" ht="15" spans="1:14">
+      <c r="A35" s="5">
         <v>2452020371</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>45</v>
+      <c r="B35" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="C35">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D35" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F35" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I35" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J35" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M35" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A36" s="9">
+        <v>15</v>
+      </c>
+      <c r="N35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" ht="15" spans="1:14">
+      <c r="A36" s="4">
         <v>2452020381</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>46</v>
+      <c r="B36" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="C36">
         <f t="shared" si="1"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D36" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E36" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G36" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J36" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A37" s="10">
+        <v>17</v>
+      </c>
+      <c r="N36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" ht="15" spans="1:14">
+      <c r="A37" s="5">
         <v>2452020390</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>47</v>
+      <c r="B37" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="C37">
         <f t="shared" si="1"/>
         <v>91</v>
       </c>
       <c r="D37" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E37" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G37" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H37" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J37" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M37" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A38" s="9">
+        <v>15</v>
+      </c>
+      <c r="N37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" ht="15" spans="1:14">
+      <c r="A38" s="4">
         <v>2452020397</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>48</v>
+      <c r="B38" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="C38">
         <f t="shared" si="1"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E38" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J38" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K38" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M38" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A39" s="10">
+        <v>15</v>
+      </c>
+      <c r="N38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" ht="15" spans="1:14">
+      <c r="A39" s="5">
         <v>2452020410</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>49</v>
+      <c r="B39" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="C39">
         <f t="shared" si="1"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D39" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E39" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F39" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I39" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J39" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M39" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A40" s="9">
+        <v>15</v>
+      </c>
+      <c r="N39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" ht="15" spans="1:14">
+      <c r="A40" s="4">
         <v>2452020421</v>
       </c>
-      <c r="B40" s="9" t="s">
-        <v>50</v>
+      <c r="B40" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="C40">
         <f t="shared" si="1"/>
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D40" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E40" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F40" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I40" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J40" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M40" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A41" s="10">
+        <v>15</v>
+      </c>
+      <c r="N40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" ht="15" spans="1:14">
+      <c r="A41" s="5">
         <v>2452020424</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>51</v>
+      <c r="B41" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C41">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
       <c r="D41" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E41" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G41" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H41" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I41" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J41" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K41" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L41" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M41" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A42" s="9">
+        <v>15</v>
+      </c>
+      <c r="N41" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" ht="15" spans="1:14">
+      <c r="A42" s="4">
         <v>2452020454</v>
       </c>
-      <c r="B42" s="9" t="s">
-        <v>52</v>
+      <c r="B42" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="C42">
         <f t="shared" si="1"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D42" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F42" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I42" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J42" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K42" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A43" s="10">
+        <v>17</v>
+      </c>
+      <c r="N42" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" ht="15" spans="1:14">
+      <c r="A43" s="5">
         <v>2452020478</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>53</v>
+      <c r="B43" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="C43">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D43" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E43" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G43" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H43" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I43" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J43" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K43" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L43" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M43" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A44" s="9">
+        <v>17</v>
+      </c>
+      <c r="N43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" ht="15" spans="1:14">
+      <c r="A44" s="4">
         <v>2452020484</v>
       </c>
-      <c r="B44" s="9" t="s">
-        <v>54</v>
+      <c r="B44" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="C44">
         <f t="shared" si="1"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D44" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E44" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F44" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G44" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H44" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I44" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J44" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K44" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M44" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A45" s="10">
+        <v>17</v>
+      </c>
+      <c r="N44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" ht="15" spans="1:14">
+      <c r="A45" s="5">
         <v>2452020759</v>
       </c>
-      <c r="B45" s="10" t="s">
-        <v>55</v>
+      <c r="B45" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="C45">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D45" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E45" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F45" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G45" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H45" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I45" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J45" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K45" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L45" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M45" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A46" s="9">
+        <v>17</v>
+      </c>
+      <c r="N45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" ht="15" spans="1:14">
+      <c r="A46" s="4">
         <v>2452020821</v>
       </c>
-      <c r="B46" s="9" t="s">
-        <v>56</v>
+      <c r="B46" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="C46">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
       <c r="D46" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E46" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F46" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H46" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I46" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J46" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K46" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M46" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A47" s="10">
+        <v>15</v>
+      </c>
+      <c r="N46" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" ht="15" spans="1:14">
+      <c r="A47" s="5">
         <v>2452020828</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>57</v>
+      <c r="B47" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="C47">
         <f t="shared" si="1"/>
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D47" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E47" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I47" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J47" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K47" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M47" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:64" ht="78" customHeight="1" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="N47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" ht="78" customHeight="1" spans="4:64">
       <c r="D48">
         <f>COUNTIF(D3:D47,"×")</f>
         <v>16</v>
@@ -2752,7 +3501,7 @@
       </c>
       <c r="N48">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O48">
         <f t="shared" si="2"/>
@@ -2955,17 +3704,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="8:15" ht="30" x14ac:dyDescent="0.4">
-      <c r="H50" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="I50" s="24"/>
-      <c r="J50" s="24"/>
-      <c r="K50" s="24"/>
-      <c r="L50" s="24"/>
-      <c r="M50" s="24"/>
-      <c r="N50" s="24"/>
-      <c r="O50" s="24"/>
+    <row r="50" ht="30" spans="8:15">
+      <c r="H50" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2974,8 +3723,7 @@
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
-  <conditionalFormatting sqref="C1:C1048576">
+  <conditionalFormatting sqref="C$1:C$1048576">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="percentile" val="20"/>
@@ -2986,546 +3734,549 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
-  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="15.625" customWidth="1"/>
     <col min="4" max="5" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="14"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="15" t="s">
+      <c r="B1" s="17"/>
+    </row>
+    <row r="2" ht="15" spans="1:5">
+      <c r="A2" s="18"/>
+      <c r="B2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-    </row>
-    <row r="3" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="17">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" ht="24.75" spans="1:4">
+      <c r="A3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="21">
         <f>100-COUNTIF(C3:AZ3,"△")*30</f>
         <v>100</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-    </row>
-    <row r="4" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="17">
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+    </row>
+    <row r="4" ht="24" spans="1:4">
+      <c r="A4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="21">
         <f t="shared" ref="B4:B49" si="0">100-COUNTIF(C4:AZ4,"△")*30</f>
         <v>100</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-    </row>
-    <row r="5" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+    </row>
+    <row r="5" ht="24" spans="1:5">
+      <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A9" s="10" t="s">
+      <c r="B5" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+    </row>
+    <row r="6" ht="24" spans="1:4">
+      <c r="A6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D9" s="18"/>
-    </row>
-    <row r="10" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
+      <c r="B6" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+    </row>
+    <row r="7" ht="15" spans="1:2">
+      <c r="A7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-    </row>
-    <row r="11" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A11" s="12" t="s">
+      <c r="B7" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="1:2">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" ht="24" spans="1:4">
+      <c r="A9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D9" s="22"/>
+    </row>
+    <row r="10" ht="24" spans="1:4">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+    </row>
+    <row r="11" ht="24" spans="1:5">
+      <c r="A11" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+    </row>
+    <row r="12" ht="24" spans="1:4">
+      <c r="A12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D12" s="22"/>
+    </row>
+    <row r="13" ht="24" spans="1:4">
+      <c r="A13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D13" s="22"/>
+    </row>
+    <row r="14" ht="24" spans="1:4">
+      <c r="A14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D14" s="22"/>
+    </row>
+    <row r="15" ht="24" spans="1:4">
+      <c r="A15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D15" s="22"/>
+    </row>
+    <row r="16" ht="24" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+    </row>
+    <row r="17" ht="24" spans="1:4">
+      <c r="A17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D17" s="22"/>
+    </row>
+    <row r="18" ht="24" spans="1:4">
+      <c r="A18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D18" s="22"/>
+    </row>
+    <row r="19" ht="24" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+    </row>
+    <row r="20" ht="24" spans="1:4">
+      <c r="A20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D20" s="22"/>
+    </row>
+    <row r="21" ht="24" spans="1:4">
+      <c r="A21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D21" s="22"/>
+    </row>
+    <row r="22" ht="15" spans="1:2">
+      <c r="A22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="1:2">
+      <c r="A23" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" ht="24" spans="1:5">
+      <c r="A24" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+    </row>
+    <row r="25" ht="24" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+    </row>
+    <row r="26" ht="24" spans="1:5">
+      <c r="A26" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+    </row>
+    <row r="27" ht="24" spans="1:5">
+      <c r="A27" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+    </row>
+    <row r="28" ht="15" spans="1:2">
+      <c r="A28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" ht="15" spans="1:2">
+      <c r="A29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" ht="24" spans="1:5">
+      <c r="A30" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+    </row>
+    <row r="31" ht="24" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+    </row>
+    <row r="32" ht="24" spans="1:4">
+      <c r="A32" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+    </row>
+    <row r="33" ht="24" spans="1:3">
+      <c r="A33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C33" s="22"/>
+    </row>
+    <row r="34" ht="24" spans="1:5">
+      <c r="A34" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+    </row>
+    <row r="35" ht="24" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+    </row>
+    <row r="36" ht="15" spans="1:2">
+      <c r="A36" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" ht="24" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+    </row>
+    <row r="38" ht="24" spans="1:5">
+      <c r="A38" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+    </row>
+    <row r="39" ht="24" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+    </row>
+    <row r="40" ht="24" spans="1:5">
+      <c r="A40" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+    </row>
+    <row r="41" ht="24" spans="1:4">
+      <c r="A41" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D41" s="22"/>
+    </row>
+    <row r="42" ht="24" spans="1:5">
+      <c r="A42" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+    </row>
+    <row r="43" ht="15" spans="1:2">
+      <c r="A43" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" ht="24" spans="1:5">
+      <c r="A44" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+    </row>
+    <row r="45" ht="24" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+    </row>
+    <row r="46" ht="24" spans="1:5">
+      <c r="A46" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+    </row>
+    <row r="47" ht="24" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+    </row>
+    <row r="48" ht="15" spans="1:2">
+      <c r="A48" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-    </row>
-    <row r="12" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D12" s="18"/>
-    </row>
-    <row r="13" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A13" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D13" s="18"/>
-    </row>
-    <row r="14" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D14" s="18"/>
-    </row>
-    <row r="15" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A15" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D15" s="18"/>
-    </row>
-    <row r="16" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-    </row>
-    <row r="17" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D17" s="18"/>
-    </row>
-    <row r="18" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D18" s="18"/>
-    </row>
-    <row r="19" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A19" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-    </row>
-    <row r="20" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A20" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D20" s="18"/>
-    </row>
-    <row r="21" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A21" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D21" s="18"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-    </row>
-    <row r="25" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A25" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-    </row>
-    <row r="26" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A26" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-    </row>
-    <row r="27" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A27" s="13" t="s">
+      <c r="B48" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" ht="15" spans="1:2">
+      <c r="A49" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A30" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-    </row>
-    <row r="31" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A31" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-    </row>
-    <row r="32" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A32" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-    </row>
-    <row r="33" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A33" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C33" s="18"/>
-    </row>
-    <row r="34" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A34" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-    </row>
-    <row r="35" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A35" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A37" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-    </row>
-    <row r="38" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A38" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-    </row>
-    <row r="39" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A39" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-    </row>
-    <row r="40" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A40" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-    </row>
-    <row r="41" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A41" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D41" s="18"/>
-    </row>
-    <row r="42" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A42" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A44" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-    </row>
-    <row r="45" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A45" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B45" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-    </row>
-    <row r="46" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A46" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-    </row>
-    <row r="47" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A47" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B47" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B48" s="17">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" s="17">
+      <c r="B49" s="21">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
@@ -3534,221 +4285,229 @@
   <mergeCells count="1">
     <mergeCell ref="A1:A2"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="28"/>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" ht="15" spans="1:3">
       <c r="A2">
         <v>4.01</v>
       </c>
       <c r="B2">
         <v>4.08</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="5"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="8"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="7"/>
-      <c r="M7" s="10"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="7"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="10"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="4"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="8"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="H9" s="11"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="4"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="2"/>
-      <c r="H10" s="12"/>
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
-      <c r="D11" s="4"/>
-      <c r="H11" s="9"/>
-      <c r="K11" s="7"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="3"/>
-      <c r="D12" s="13"/>
-      <c r="K12" s="4"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="8"/>
-      <c r="D13" s="3"/>
-      <c r="K13" s="10"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="D14" s="2"/>
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="D15" s="4"/>
-      <c r="K15" s="7"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="D16" s="7"/>
-      <c r="K16" s="4"/>
-    </row>
-    <row r="17" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D17" s="3"/>
-      <c r="K17" s="7"/>
-    </row>
-    <row r="18" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D18" s="2"/>
-      <c r="K18" s="4"/>
-    </row>
-    <row r="19" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K19" s="7"/>
-    </row>
-    <row r="20" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K20" s="4"/>
-    </row>
-    <row r="21" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K21" s="7"/>
-    </row>
-    <row r="22" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K22" s="4"/>
-    </row>
-    <row r="23" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K23" s="7"/>
-    </row>
-    <row r="24" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K24" s="9"/>
-    </row>
-    <row r="25" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K25" s="7"/>
-    </row>
-    <row r="26" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K26" s="4"/>
-    </row>
-    <row r="27" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K27" s="7"/>
-    </row>
-    <row r="28" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K28" s="4"/>
-    </row>
-    <row r="29" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K29" s="6"/>
-    </row>
-    <row r="30" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K30" s="7"/>
-    </row>
-    <row r="31" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="K31" s="9"/>
+      <c r="C2">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="A3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+    </row>
+    <row r="4" ht="15" spans="1:13">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+    </row>
+    <row r="5" ht="15" spans="1:13">
+      <c r="A5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" ht="15" spans="1:13">
+      <c r="A6" s="9"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+    </row>
+    <row r="7" ht="15" spans="1:13">
+      <c r="A7" s="12"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="11"/>
+      <c r="M7" s="5"/>
+    </row>
+    <row r="8" ht="15" spans="1:11">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="11"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="5"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" ht="15" spans="1:11">
+      <c r="A9" s="12"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="H9" s="13"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" ht="15" spans="1:11">
+      <c r="A10" s="6"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="7"/>
+      <c r="H10" s="14"/>
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" ht="15" spans="1:11">
+      <c r="A11" s="14"/>
+      <c r="D11" s="8"/>
+      <c r="H11" s="4"/>
+      <c r="K11" s="11"/>
+    </row>
+    <row r="12" ht="15" spans="1:11">
+      <c r="A12" s="6"/>
+      <c r="D12" s="15"/>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" ht="15" spans="1:11">
+      <c r="A13" s="12"/>
+      <c r="D13" s="6"/>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" ht="15" spans="4:11">
+      <c r="D14" s="7"/>
+      <c r="K14" s="8"/>
+    </row>
+    <row r="15" ht="15" spans="4:11">
+      <c r="D15" s="8"/>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" ht="15" spans="4:11">
+      <c r="D16" s="11"/>
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" ht="15" spans="4:11">
+      <c r="D17" s="6"/>
+      <c r="K17" s="11"/>
+    </row>
+    <row r="18" ht="15" spans="4:11">
+      <c r="D18" s="7"/>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" ht="15" spans="11:11">
+      <c r="K19" s="11"/>
+    </row>
+    <row r="20" ht="15" spans="11:11">
+      <c r="K20" s="8"/>
+    </row>
+    <row r="21" ht="15" spans="11:11">
+      <c r="K21" s="11"/>
+    </row>
+    <row r="22" ht="15" spans="11:11">
+      <c r="K22" s="8"/>
+    </row>
+    <row r="23" ht="15" spans="11:11">
+      <c r="K23" s="11"/>
+    </row>
+    <row r="24" ht="15" spans="11:11">
+      <c r="K24" s="4"/>
+    </row>
+    <row r="25" ht="15" spans="11:11">
+      <c r="K25" s="11"/>
+    </row>
+    <row r="26" ht="15" spans="11:11">
+      <c r="K26" s="8"/>
+    </row>
+    <row r="27" ht="15" spans="11:11">
+      <c r="K27" s="11"/>
+    </row>
+    <row r="28" ht="15" spans="11:11">
+      <c r="K28" s="8"/>
+    </row>
+    <row r="29" ht="15" spans="11:11">
+      <c r="K29" s="10"/>
+    </row>
+    <row r="30" ht="15" spans="11:11">
+      <c r="K30" s="11"/>
+    </row>
+    <row r="31" ht="15" spans="11:11">
+      <c r="K31" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>